--- a/logs/reduced_features/3_head_model_option_3/3_head_model_option_3.xlsx
+++ b/logs/reduced_features/3_head_model_option_3/3_head_model_option_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/reduced_features/3_head_model_option_3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_6B1570ABD3C05F501F983E11595ED87656C43896" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B7E8D5-725B-4C53-9E50-344179224D24}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_6B1570ABD3C05F501F983E11595ED87656C43896" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73886633-64CE-4E14-B313-FA70EC1CAD71}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="17" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2825" uniqueCount="455">
   <si>
     <t>date</t>
   </si>
@@ -1384,6 +1384,12 @@
   <si>
     <t>04-14_11-10-26_multihead_3heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
   </si>
+  <si>
+    <t>14/04/2026 13:43:02</t>
+  </si>
+  <si>
+    <t>04-14_13-43-02_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -1437,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1449,7 +1455,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1512,7 +1517,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46126.568445717596" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="159" xr:uid="{3058419C-445B-43A9-B9BC-AAE7756FE797}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46126.644611574076" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="160" xr:uid="{3058419C-445B-43A9-B9BC-AAE7756FE797}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -1783,7 +1788,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="159">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="160">
   <r>
     <s v="02/04/2026 17:14:14"/>
     <s v="04-02_17-14-14_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
@@ -14186,11 +14191,89 @@
     <n v="577.63868366673239"/>
     <n v="-0.64406151965319891"/>
   </r>
+  <r>
+    <s v="14/04/2026 13:43:02"/>
+    <s v="04-14_13-43-02_multihead_3heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['sv', 'rarad'], ['wv', 'yr', 'rarad'], ['ya', 'rarad']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <b v="1"/>
+    <b v="0"/>
+    <b v="0"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['wv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 2, -1, 1, 2, -1]}, {'features': ['ya', 'rarad'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [1, 0, -1]}]"/>
+    <n v="3"/>
+    <s v="serial"/>
+    <s v="effsu2"/>
+    <s v="lin"/>
+    <n v="1"/>
+    <x v="12"/>
+    <b v="0"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="256"/>
+    <s v="[0.1, 0.001]"/>
+    <n v="0.15"/>
+    <s v="[1.0, 1.0, 1.0, 1.0]"/>
+    <n v="160"/>
+    <n v="40"/>
+    <n v="120"/>
+    <n v="9.3876537245818903E-2"/>
+    <n v="28.683674250727229"/>
+    <n v="0.81419034578160709"/>
+    <n v="-2.487424252616397"/>
+    <n v="47.089741922409019"/>
+    <n v="0.76142692119966937"/>
+    <n v="47.089741922409019"/>
+    <n v="47.089741922409019"/>
+    <n v="0.76142692119966937"/>
+    <n v="124.96548920278509"/>
+    <n v="-1.40489007057226"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="1.11149114288867E-2"/>
+    <n v="0.91929137190667642"/>
+    <n v="1.11149114288867E-2"/>
+    <n v="1.11149114288867E-2"/>
+    <n v="0.91929137190667642"/>
+    <n v="0.8502113750694279"/>
+    <n v="-5.1736338710586223"/>
+    <n v="4.4107504556798502E-2"/>
+    <n v="0.84717691728020894"/>
+    <n v="4.4107504556798502E-2"/>
+    <n v="4.4107504556798502E-2"/>
+    <n v="0.84717691728020894"/>
+    <n v="0.32647205928283241"/>
+    <n v="-0.13115595685611359"/>
+    <n v="4.6067406822556098E-2"/>
+    <n v="0.81505393281596628"/>
+    <n v="4.6067406822556098E-2"/>
+    <n v="4.6067406822556098E-2"/>
+    <n v="0.81505393281596628"/>
+    <n v="0.2231955440407826"/>
+    <n v="0.1039404878519897"/>
+    <n v="188.25767786682741"/>
+    <n v="0.46418546279582568"/>
+    <n v="188.25767786682741"/>
+    <n v="188.25767786682741"/>
+    <n v="0.46418546279582568"/>
+    <n v="498.46207783274889"/>
+    <n v="-0.41871094222631861"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D91C8A2E-0F35-402C-99B3-F20C1917184D}" name="TablaDinámica1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D91C8A2E-0F35-402C-99B3-F20C1917184D}" name="TablaDinámica1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:L20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
@@ -14434,7 +14517,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14F0F05E-9278-4D29-86F2-A4F2A7443150}" name="Tabla1" displayName="Tabla1" ref="A1:BX160" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14F0F05E-9278-4D29-86F2-A4F2A7443150}" name="Tabla1" displayName="Tabla1" ref="A1:BX161" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BX124">
     <sortCondition descending="1" ref="W1:W158"/>
   </sortState>
@@ -14805,7 +14888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BX160"/>
+  <dimension ref="A1:BX161"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.109375" customWidth="1"/>
@@ -51199,6 +51282,233 @@
         <v>-0.64406151965319891</v>
       </c>
     </row>
+    <row r="161" spans="1:76" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>453</v>
+      </c>
+      <c r="B161" t="s">
+        <v>454</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>78</v>
+      </c>
+      <c r="E161" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161">
+        <v>16590</v>
+      </c>
+      <c r="G161">
+        <v>4.5</v>
+      </c>
+      <c r="H161" t="s">
+        <v>80</v>
+      </c>
+      <c r="I161" t="s">
+        <v>81</v>
+      </c>
+      <c r="J161">
+        <v>5</v>
+      </c>
+      <c r="K161">
+        <v>5</v>
+      </c>
+      <c r="L161" t="s">
+        <v>82</v>
+      </c>
+      <c r="M161" t="b">
+        <v>1</v>
+      </c>
+      <c r="N161" t="b">
+        <v>0</v>
+      </c>
+      <c r="O161" t="b">
+        <v>0</v>
+      </c>
+      <c r="P161" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>144</v>
+      </c>
+      <c r="R161">
+        <v>3</v>
+      </c>
+      <c r="S161" t="s">
+        <v>85</v>
+      </c>
+      <c r="T161" t="s">
+        <v>86</v>
+      </c>
+      <c r="U161" t="s">
+        <v>87</v>
+      </c>
+      <c r="V161">
+        <v>1</v>
+      </c>
+      <c r="W161" t="s">
+        <v>145</v>
+      </c>
+      <c r="X161" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z161">
+        <v>4000</v>
+      </c>
+      <c r="AA161">
+        <v>4000</v>
+      </c>
+      <c r="AC161">
+        <v>256</v>
+      </c>
+      <c r="AD161" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE161">
+        <v>0.15</v>
+      </c>
+      <c r="AF161" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG161">
+        <v>160</v>
+      </c>
+      <c r="AH161">
+        <v>40</v>
+      </c>
+      <c r="AI161">
+        <v>120</v>
+      </c>
+      <c r="AJ161">
+        <v>9.3876537245818903E-2</v>
+      </c>
+      <c r="AK161">
+        <v>28.683674250727229</v>
+      </c>
+      <c r="AL161">
+        <v>0.81419034578160709</v>
+      </c>
+      <c r="AM161">
+        <v>-2.487424252616397</v>
+      </c>
+      <c r="AN161">
+        <v>47.089741922409019</v>
+      </c>
+      <c r="AO161">
+        <v>0.76142692119966937</v>
+      </c>
+      <c r="AP161">
+        <v>47.089741922409019</v>
+      </c>
+      <c r="AQ161">
+        <v>47.089741922409019</v>
+      </c>
+      <c r="AR161">
+        <v>0.76142692119966937</v>
+      </c>
+      <c r="AS161">
+        <v>124.96548920278509</v>
+      </c>
+      <c r="AT161">
+        <v>-1.40489007057226</v>
+      </c>
+      <c r="AU161">
+        <v>0.8</v>
+      </c>
+      <c r="AV161" t="s">
+        <v>92</v>
+      </c>
+      <c r="AW161">
+        <v>1.11149114288867E-2</v>
+      </c>
+      <c r="AX161">
+        <v>0.91929137190667642</v>
+      </c>
+      <c r="AY161">
+        <v>1.11149114288867E-2</v>
+      </c>
+      <c r="AZ161">
+        <v>1.11149114288867E-2</v>
+      </c>
+      <c r="BA161">
+        <v>0.91929137190667642</v>
+      </c>
+      <c r="BB161">
+        <v>0.8502113750694279</v>
+      </c>
+      <c r="BC161">
+        <v>-5.1736338710586223</v>
+      </c>
+      <c r="BD161">
+        <v>4.4107504556798502E-2</v>
+      </c>
+      <c r="BE161">
+        <v>0.84717691728020894</v>
+      </c>
+      <c r="BF161">
+        <v>4.4107504556798502E-2</v>
+      </c>
+      <c r="BG161">
+        <v>4.4107504556798502E-2</v>
+      </c>
+      <c r="BH161">
+        <v>0.84717691728020894</v>
+      </c>
+      <c r="BI161">
+        <v>0.32647205928283241</v>
+      </c>
+      <c r="BJ161">
+        <v>-0.13115595685611359</v>
+      </c>
+      <c r="BK161">
+        <v>4.6067406822556098E-2</v>
+      </c>
+      <c r="BL161">
+        <v>0.81505393281596628</v>
+      </c>
+      <c r="BM161">
+        <v>4.6067406822556098E-2</v>
+      </c>
+      <c r="BN161">
+        <v>4.6067406822556098E-2</v>
+      </c>
+      <c r="BO161">
+        <v>0.81505393281596628</v>
+      </c>
+      <c r="BP161">
+        <v>0.2231955440407826</v>
+      </c>
+      <c r="BQ161">
+        <v>0.1039404878519897</v>
+      </c>
+      <c r="BR161">
+        <v>188.25767786682741</v>
+      </c>
+      <c r="BS161">
+        <v>0.46418546279582568</v>
+      </c>
+      <c r="BT161">
+        <v>188.25767786682741</v>
+      </c>
+      <c r="BU161">
+        <v>188.25767786682741</v>
+      </c>
+      <c r="BV161">
+        <v>0.46418546279582568</v>
+      </c>
+      <c r="BW161">
+        <v>498.46207783274889</v>
+      </c>
+      <c r="BX161">
+        <v>-0.41871094222631861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
@@ -51268,37 +51578,37 @@
       <c r="A4" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.85004817070143823</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>0.91399544647769593</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>0.87255556176688742</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>0.90754625721534854</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4">
         <v>0.70609541734581982</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4">
         <v>-0.82432318034951346</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>-2.3664948389735776</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.44722224493255514</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>0.63066899993328662</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>-2.0086891272903147</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4">
         <v>10</v>
       </c>
     </row>
@@ -51306,37 +51616,37 @@
       <c r="A5" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>0.84568792262967796</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5">
         <v>0.90864512808615139</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>0.90674182638239853</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>0.86174099773246748</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>0.70562373831769309</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>-0.73859858709812032</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>-1.5519322940536973</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.22932977684795347</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>0.27224943217215813</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5">
         <v>-1.9040412633589021</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5">
         <v>10</v>
       </c>
     </row>
@@ -51344,37 +51654,37 @@
       <c r="A6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>0.8408755073281059</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6">
         <v>0.91556746907180586</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>0.85986412036757431</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>0.89128211585696471</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6">
         <v>0.69678832401607804</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6">
         <v>-0.73134352447591788</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>-2.2072679103891333</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.68260090047308286</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>0.77928166805852128</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6">
         <v>-2.1799887560461322</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6">
         <v>10</v>
       </c>
     </row>
@@ -51382,37 +51692,37 @@
       <c r="A7" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>0.81772974154029721</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>0.91813573590506437</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>0.81013837122367838</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>0.85224378937993728</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>0.69040106965250714</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7">
         <v>-0.63546100747915735</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>-1.928469481354582</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.6719189778221043</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.79453358786785133</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7">
         <v>-2.0798271142519993</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7">
         <v>10</v>
       </c>
     </row>
@@ -51420,37 +51730,37 @@
       <c r="A8" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>0.77737829019061944</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>0.90718572418902477</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>0.87889884478233626</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>0.90222730027713016</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>0.42120129151398683</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>-0.21180529324241038</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>-1.8132884664746509</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>0.56370420230929352</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>0.73249101410197615</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8">
         <v>-0.33012792290625753</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8">
         <v>10</v>
       </c>
     </row>
@@ -51458,75 +51768,75 @@
       <c r="A9" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B9" s="5">
-        <v>0.76772165748114396</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.90208871191421758</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.89846873961968776</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.85526445414142438</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.41506472424924579</v>
-      </c>
-      <c r="G9" s="5">
-        <v>-0.652729122026523</v>
-      </c>
-      <c r="H9" s="5">
-        <v>-2.4258883620767202</v>
-      </c>
-      <c r="I9" s="5">
-        <v>9.930869117104188E-2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0.16772332391235656</v>
-      </c>
-      <c r="K9" s="5">
-        <v>-0.45206014111277182</v>
-      </c>
-      <c r="L9" s="5">
-        <v>9</v>
+      <c r="B9">
+        <v>0.76709218385299649</v>
+      </c>
+      <c r="C9">
+        <v>0.90380897791346337</v>
+      </c>
+      <c r="D9">
+        <v>0.89333955738573978</v>
+      </c>
+      <c r="E9">
+        <v>0.85124340200887849</v>
+      </c>
+      <c r="F9">
+        <v>0.41997679810390381</v>
+      </c>
+      <c r="G9">
+        <v>-0.7279452168810967</v>
+      </c>
+      <c r="H9">
+        <v>-2.7006629129749102</v>
+      </c>
+      <c r="I9">
+        <v>7.626222636832633E-2</v>
+      </c>
+      <c r="J9">
+        <v>0.16134504030631985</v>
+      </c>
+      <c r="K9">
+        <v>-0.44872522122412645</v>
+      </c>
+      <c r="L9">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>0.75937608190282169</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>0.5683370412215446</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>0.8760114612992933</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>0.90785295566949975</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>0.68530286942094931</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10">
         <v>-7.7158123720002345E-2</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>0.23983556641526321</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10">
         <v>0.51926597124137852</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>0.71126543442613299</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10">
         <v>-1.7789994669627838</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10">
         <v>10</v>
       </c>
     </row>
@@ -51534,37 +51844,37 @@
       <c r="A11" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>0.75451005965839324</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>0.90733511530557998</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>0.83940846074646591</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>0.87774787740903992</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>0.39354878517248582</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>-7.4252534001158998E-2</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>-1.5569123291040483</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11">
         <v>0.65891892277797104</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>0.78349338341136299</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11">
         <v>-0.18251011308992149</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11">
         <v>10</v>
       </c>
     </row>
@@ -51572,37 +51882,37 @@
       <c r="A12" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12">
         <v>0.75280980233715444</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>0.56827782330184018</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>0.89401613225141996</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>0.85509505231684346</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>0.69385020147851417</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12">
         <v>-0.36632655635160749</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12">
         <v>0.22908927316729319</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12">
         <v>0.16094297724634415</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12">
         <v>0.16736794356689416</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12">
         <v>-2.0227064193869699</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12">
         <v>10</v>
       </c>
     </row>
@@ -51610,37 +51920,37 @@
       <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13">
         <v>0.74813795126523042</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>0.56933910776662644</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>0.84628127082046123</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>0.87905882483269759</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>0.69787260164113563</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13">
         <v>-9.0850445595681048E-2</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13">
         <v>0.22178232661296776</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13">
         <v>0.64356806139376832</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13">
         <v>0.75681879998895529</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13">
         <v>-1.9855709703784128</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13">
         <v>10</v>
       </c>
     </row>
@@ -51648,37 +51958,37 @@
       <c r="A14" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>0.74636142851089504</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>0.91222222775551065</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14">
         <v>0.82394566111701018</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14">
         <v>0.85090064904202067</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14">
         <v>0.39837717612903628</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14">
         <v>-0.22579516987124312</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14">
         <v>-2.1017995665177991</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14">
         <v>0.64739328601917245</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14">
         <v>0.76362158285718873</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14">
         <v>-0.21239598184353298</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14">
         <v>10</v>
       </c>
     </row>
@@ -51686,37 +51996,37 @@
       <c r="A15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>0.73342499467853162</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>0.56989384601384008</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15">
         <v>0.82371809009591068</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15">
         <v>0.85927213860285945</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15">
         <v>0.68081590400151559</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15">
         <v>-6.8528586386267437E-2</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15">
         <v>0.22281413832419425</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15">
         <v>0.67492844997350099</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15">
         <v>0.7813705017999979</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15">
         <v>-1.9532274356427646</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15">
         <v>10</v>
       </c>
     </row>
@@ -51724,37 +52034,37 @@
       <c r="A16" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>0.67552642044055988</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>0.53880053490958435</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16">
         <v>0.84352264828064116</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16">
         <v>0.87040963728651044</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16">
         <v>0.44937286128550291</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16">
         <v>0.27650659146898549</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16">
         <v>0.19250379859046698</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16">
         <v>0.58123466237637511</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16">
         <v>0.69661703330251235</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16">
         <v>-0.36432912839341591</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16">
         <v>10</v>
       </c>
     </row>
@@ -51762,37 +52072,37 @@
       <c r="A17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>0.67095186450527022</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>0.5363847353662885</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17">
         <v>0.89169698251651508</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17">
         <v>0.85260432164892319</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17">
         <v>0.40312141848935357</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17">
         <v>-0.10751911115501822</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17">
         <v>0.22317030678205083</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17">
         <v>1.2033526821761264E-2</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17">
         <v>8.2797256303203809E-2</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17">
         <v>-0.74807753452710357</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17">
         <v>10</v>
       </c>
     </row>
@@ -51800,37 +52110,37 @@
       <c r="A18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>0.67075506387227979</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>0.55977851202809137</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18">
         <v>0.81777821858818722</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18">
         <v>0.85493765961905643</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18">
         <v>0.45052586525378285</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18">
         <v>0.30148221955554244</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18">
         <v>0.18010866380989959</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18">
         <v>0.67207102198930735</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18">
         <v>0.78262762931076257</v>
       </c>
-      <c r="K18" s="5">
+      <c r="K18">
         <v>-0.42887843688779875</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18">
         <v>10</v>
       </c>
     </row>
@@ -51838,37 +52148,37 @@
       <c r="A19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19">
         <v>0.66899111994476834</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>0.54503510326360483</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19">
         <v>0.86804215132362894</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19">
         <v>0.89973344370172792</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19">
         <v>0.36315378149011196</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19">
         <v>0.25236577858765902</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19">
         <v>0.20318594098042811</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19">
         <v>0.53899445893053177</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19">
         <v>0.7338777703675764</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19">
         <v>-0.46659505592790584</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19">
         <v>10</v>
       </c>
     </row>
@@ -51876,38 +52186,38 @@
       <c r="A20" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B20" s="5">
-        <v>0.75493798183893523</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.73275555920660651</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.85919758913334154</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.87373528486278695</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.55406349415300582</v>
-      </c>
-      <c r="G20" s="5">
-        <v>-0.24585306540489202</v>
-      </c>
-      <c r="H20" s="5">
-        <v>-0.88031285522352032</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0.49015756372383895</v>
-      </c>
-      <c r="J20" s="5">
-        <v>0.60503352383581788</v>
-      </c>
-      <c r="K20" s="5">
-        <v>-1.1982904939557044</v>
-      </c>
-      <c r="L20" s="5">
-        <v>159</v>
+      <c r="B20">
+        <v>0.75497853770993983</v>
+      </c>
+      <c r="C20">
+        <v>0.73392140803598205</v>
+      </c>
+      <c r="D20">
+        <v>0.85912245993425951</v>
+      </c>
+      <c r="E20">
+        <v>0.87336852641249441</v>
+      </c>
+      <c r="F20">
+        <v>0.55350175645702349</v>
+      </c>
+      <c r="G20">
+        <v>-0.25309704668718813</v>
+      </c>
+      <c r="H20">
+        <v>-0.90714611157248992</v>
+      </c>
+      <c r="I20">
+        <v>0.4862743542202142</v>
+      </c>
+      <c r="J20">
+        <v>0.60190169236091884</v>
+      </c>
+      <c r="K20">
+        <v>-1.1934181217573958</v>
+      </c>
+      <c r="L20">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
